--- a/src/index spreadsheet/CONFIG defaults.xlsx
+++ b/src/index spreadsheet/CONFIG defaults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacomostert/wp43s/src/index spreadsheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB65CC0-66CF-1049-85FE-CC1CADFBFB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A17667-D90C-5142-956F-69BAABAE2262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2780" yWindow="1500" windowWidth="28040" windowHeight="17440" xr2:uid="{6E744F0C-E143-0F4E-B8F2-0B8E6327768E}"/>
+    <workbookView xWindow="5560" yWindow="2960" windowWidth="28040" windowHeight="17440" xr2:uid="{6E744F0C-E143-0F4E-B8F2-0B8E6327768E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="117">
   <si>
     <t>//TVM</t>
   </si>
@@ -392,7 +392,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -442,6 +442,11 @@
     <font>
       <sz val="12"/>
       <color rgb="FF0070C0"/>
+      <name val="C47__StandardFont StandardFont"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="C47__StandardFont StandardFont"/>
     </font>
   </fonts>
@@ -501,7 +506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -549,11 +554,21 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -899,7 +914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91A1B956-3A7D-A54E-9169-CB58BF048D40}">
-  <dimension ref="A1:N415"/>
+  <dimension ref="A1:N413"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.83203125" style="1" bestFit="1" customWidth="1"/>
@@ -1019,11 +1034,11 @@
       <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>10</v>
+      <c r="E3" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>12</v>
@@ -1046,7 +1061,7 @@
 H3&amp;", "&amp;REPT(" ",$H$1-LEN(H3))&amp;
 I3&amp;", "&amp;REPT(" ",$I$1-LEN(I3))&amp;
 J3</f>
-        <v xml:space="preserve">InputDefaultDataType,                xxx,        xxx,                            ID_DP,           xxx,                  xxx,                    ID_43S,          xxx,             xxx,                  </v>
+        <v xml:space="preserve">InputDefaultDataType,                xxx,        xxx,                            ID_DP,           ID_43S,               ID_43S,                 ID_43S,          xxx,             xxx,                  </v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15">
@@ -1173,11 +1188,11 @@
       <c r="D7" s="1">
         <v>0</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>10</v>
+      <c r="E7" s="17">
+        <v>1</v>
+      </c>
+      <c r="F7" s="17">
+        <v>1</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -1191,7 +1206,7 @@
       <c r="K7" s="8"/>
       <c r="N7" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">MymB,                                xxx,        1,                              0,               xxx,                  xxx,                    1,               xxx,             xxx,                  </v>
+        <v xml:space="preserve">MymB,                                xxx,        1,                              0,               1,                    1,                      1,               xxx,             xxx,                  </v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15">
@@ -1207,11 +1222,11 @@
       <c r="D8" s="1">
         <v>0</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>10</v>
+      <c r="E8" s="17">
+        <v>0</v>
+      </c>
+      <c r="F8" s="17">
+        <v>0</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1225,7 +1240,7 @@
       <c r="K8" s="8"/>
       <c r="N8" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">HomeB,                               xxx,        0,                              0,               xxx,                  xxx,                    0,               xxx,             xxx,                  </v>
+        <v xml:space="preserve">HomeB,                               xxx,        0,                              0,               0,                    0,                      0,               xxx,             xxx,                  </v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15">
@@ -1241,11 +1256,11 @@
       <c r="D9" s="1">
         <v>99</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>10</v>
+      <c r="E9" s="17">
+        <v>6145</v>
+      </c>
+      <c r="F9" s="17">
+        <v>6145</v>
       </c>
       <c r="G9" s="1">
         <v>6145</v>
@@ -1259,7 +1274,7 @@
       <c r="K9" s="8"/>
       <c r="N9" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">RNG,                                 xxx,        6145,                           99,              xxx,                  xxx,                    6145,            xxx,             xxx,                  </v>
+        <v xml:space="preserve">RNG,                                 xxx,        6145,                           99,              6145,                 6145,                   6145,            xxx,             xxx,                  </v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15">
@@ -1275,11 +1290,11 @@
       <c r="D10" s="1">
         <v>16</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>10</v>
+      <c r="E10" s="17">
+        <v>0</v>
+      </c>
+      <c r="F10" s="17">
+        <v>0</v>
       </c>
       <c r="G10" s="1">
         <v>34</v>
@@ -1293,7 +1308,7 @@
       <c r="K10" s="8"/>
       <c r="N10" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">SDIGS,                               xxx,        0,                              16,              xxx,                  xxx,                    34,              xxx,             xxx,                  </v>
+        <v xml:space="preserve">SDIGS,                               xxx,        0,                              16,              0,                    0,                      34,              xxx,             xxx,                  </v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15">
@@ -1309,11 +1324,11 @@
       <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>10</v>
+      <c r="E11" s="17">
+        <v>4</v>
+      </c>
+      <c r="F11" s="17">
+        <v>4</v>
       </c>
       <c r="G11" s="1">
         <v>4</v>
@@ -1327,7 +1342,7 @@
       <c r="K11" s="8"/>
       <c r="N11" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">DSTACK,                              xxx,        4,                              1,               xxx,                  xxx,                    4,               xxx,             xxx,                  </v>
+        <v xml:space="preserve">DSTACK,                              xxx,        4,                              1,               4,                    4,                      4,               xxx,             xxx,                  </v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15">
@@ -1343,11 +1358,11 @@
       <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>10</v>
+      <c r="E12" s="17">
+        <v>4</v>
+      </c>
+      <c r="F12" s="17">
+        <v>4</v>
       </c>
       <c r="G12" s="1">
         <v>4</v>
@@ -1361,7 +1376,7 @@
       <c r="K12" s="8"/>
       <c r="N12" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">CACHEDDSTACK,                        xxx,        4,                              1,               xxx,                  xxx,                    4,               xxx,             xxx,                  </v>
+        <v xml:space="preserve">CACHEDDSTACK,                        xxx,        4,                              1,               4,                    4,                      4,               xxx,             xxx,                  </v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15">
@@ -1411,11 +1426,11 @@
       <c r="D14" s="1">
         <v>3</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>10</v>
+      <c r="E14" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="16">
+        <v>3</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>15</v>
@@ -1429,7 +1444,7 @@
       <c r="K14" s="8"/>
       <c r="N14" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">IPGRP,                               xxx,        3,                              3,               xxx,                  xxx,                    _gprl,           xxx,             xxx,                  </v>
+        <v xml:space="preserve">IPGRP,                               xxx,        3,                              3,               _gprl,                3,                      _gprl,           xxx,             xxx,                  </v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15">
@@ -1445,11 +1460,11 @@
       <c r="D15" s="1">
         <v>3</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>10</v>
+      <c r="E15" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="16">
+        <v>3</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>16</v>
@@ -1463,7 +1478,7 @@
       <c r="K15" s="8"/>
       <c r="N15" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">FPGRP,                               xxx,        3,                              3,               xxx,                  xxx,                    _gprr,           xxx,             xxx,                  </v>
+        <v xml:space="preserve">FPGRP,                               xxx,        3,                              3,               _gprr,                3,                      _gprr,           xxx,             xxx,                  </v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15">
@@ -1479,11 +1494,11 @@
       <c r="D16" s="1">
         <v>0</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>10</v>
+      <c r="E16" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="16">
+        <v>0</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>17</v>
@@ -1497,7 +1512,7 @@
       <c r="K16" s="8"/>
       <c r="N16" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">IPGRP1,                              xxx,        0,                              0,               xxx,                  xxx,                    _gpr1,           xxx,             xxx,                  </v>
+        <v xml:space="preserve">IPGRP1,                              xxx,        0,                              0,               _gpr1,                0,                      _gpr1,           xxx,             xxx,                  </v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15">
@@ -1513,8 +1528,8 @@
       <c r="D17" s="1">
         <v>0</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>10</v>
+      <c r="E17" s="17" t="s">
+        <v>18</v>
       </c>
       <c r="F17" s="16">
         <v>1</v>
@@ -1531,7 +1546,7 @@
       <c r="K17" s="8"/>
       <c r="N17" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">IPGRP1x,                             xxx,        0,                              0,               xxx,                  1,                      _gpr1x,          xxx,             xxx,                  </v>
+        <v xml:space="preserve">IPGRP1x,                             xxx,        0,                              0,               _gpr1x,               1,                      _gpr1x,          xxx,             xxx,                  </v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15">
@@ -1547,11 +1562,11 @@
       <c r="D18" s="1">
         <v>0</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>10</v>
+      <c r="E18" s="17">
+        <v>1</v>
+      </c>
+      <c r="F18" s="17">
+        <v>1</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -1565,7 +1580,7 @@
       <c r="K18" s="8"/>
       <c r="N18" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">ERPN,                                xxx,        1,                              0,               xxx,                  xxx,                    1,               xxx,             xxx,                  </v>
+        <v xml:space="preserve">ERPN,                                xxx,        1,                              0,               1,                    1,                      1,               xxx,             xxx,                  </v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15">
@@ -1581,11 +1596,11 @@
       <c r="D19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>10</v>
+      <c r="E19" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>20</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>20</v>
@@ -1599,7 +1614,7 @@
       <c r="K19" s="8"/>
       <c r="N19" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">fgLongPressSetting,                  xxx,        xxx,                            RB_FGLNOFF,      xxx,                  xxx,                    RB_FGLNFUL,      xxx,             xxx,                  </v>
+        <v xml:space="preserve">fgLongPressSetting,                  xxx,        xxx,                            RB_FGLNOFF,      RB_FGLNFUL,           RB_FGLNFUL,             RB_FGLNFUL,      xxx,             xxx,                  </v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15">
@@ -1717,8 +1732,8 @@
       <c r="D23" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>10</v>
+      <c r="E23" s="17">
+        <v>64</v>
       </c>
       <c r="F23" s="16">
         <v>9999</v>
@@ -1735,7 +1750,7 @@
       <c r="K23" s="8"/>
       <c r="N23" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">DenMaX,                              xxx,        64,                             xxx,             xxx,                  9999,                   64,              xxx,             xxx,                  </v>
+        <v xml:space="preserve">DenMaX,                              xxx,        64,                             xxx,             64,                   9999,                   64,              xxx,             xxx,                  </v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15">
@@ -2189,7 +2204,7 @@
         <v>34</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>34</v>
@@ -2206,7 +2221,7 @@
       <c r="K36" s="8"/>
       <c r="N36" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>2,                                   xxx,        xxx,                            SS_4,            SS_8,                 xxx,                    SS_8,            xxx,             xxx,                  //SetSetting</v>
+        <v>2,                                   xxx,        xxx,                            SS_4,            SS_8,                 SS_8,                   SS_8,            xxx,             xxx,                  //SetSetting</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="15">
@@ -2226,7 +2241,7 @@
         <v>37</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>37</v>
@@ -2243,7 +2258,7 @@
       <c r="K37" s="8"/>
       <c r="N37" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>2,                                   xxx,        xxx,                            ITM_CPXRES0,     ITM_CPXRES1,          xxx,                    ITM_CPXRES1,     xxx,             xxx,                  //SetSetting</v>
+        <v>2,                                   xxx,        xxx,                            ITM_CPXRES0,     ITM_CPXRES1,          ITM_CPXRES1,            ITM_CPXRES1,     xxx,             xxx,                  //SetSetting</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="15">
@@ -2263,7 +2278,7 @@
         <v>39</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>39</v>
@@ -2280,7 +2295,7 @@
       <c r="K38" s="8"/>
       <c r="N38" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>2,                                   xxx,        xxx,                            ITM_SPCRES0,     ITM_SPCRES1,          xxx,                    ITM_SPCRES1,     xxx,             xxx,                  //SetSetting</v>
+        <v>2,                                   xxx,        xxx,                            ITM_SPCRES0,     ITM_SPCRES1,          ITM_SPCRES1,            ITM_SPCRES1,     xxx,             xxx,                  //SetSetting</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15">
@@ -2296,8 +2311,8 @@
       <c r="D39" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>10</v>
+      <c r="E39" s="17" t="s">
+        <v>40</v>
       </c>
       <c r="F39" s="16" t="s">
         <v>40</v>
@@ -2317,7 +2332,7 @@
       <c r="K39" s="8"/>
       <c r="N39" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>2,                                   xxx,        xxx,                            xxx,             xxx,                  JC_IRFRAC,              xxx,             xxx,             xxx,                  //SetSetting</v>
+        <v>2,                                   xxx,        xxx,                            xxx,             JC_IRFRAC,            JC_IRFRAC,              xxx,             xxx,             xxx,                  //SetSetting</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="15">
@@ -2384,12 +2399,12 @@
         <v>10</v>
       </c>
       <c r="J41" s="1" t="str">
-        <f t="shared" ref="J41:J91" si="2">IF(B41=0,"// Clear flag "&amp;L41,"// Set flag  "&amp;L41)</f>
+        <f t="shared" ref="J41:J89" si="2">IF(B41=0,"// Clear flag "&amp;L41,"// Set flag  "&amp;L41)</f>
         <v>// Clear flag FLAG_FRCYC</v>
       </c>
       <c r="K41" s="8"/>
       <c r="L41" s="8" t="str">
-        <f t="shared" ref="L41:L72" si="3">IF(NOT(C41="xxx"),C41,IF(NOT(D41="xxx"),D41,IF(NOT(E41="xxx"),E41,IF(NOT(F41="xxx"),F41,IF(NOT(G41="xxx"),G41,IF(NOT(H41="xxx"),H41,IF(NOT(I41="xxx"),I41)))))))</f>
+        <f t="shared" ref="L41:L70" si="3">IF(NOT(C41="xxx"),C41,IF(NOT(D41="xxx"),D41,IF(NOT(E41="xxx"),E41,IF(NOT(F41="xxx"),F41,IF(NOT(G41="xxx"),G41,IF(NOT(H41="xxx"),H41,IF(NOT(I41="xxx"),I41)))))))</f>
         <v>FLAG_FRCYC</v>
       </c>
       <c r="N41" s="6" t="str">
@@ -2662,8 +2677,8 @@
       <c r="D48" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>10</v>
+      <c r="E48" s="17" t="s">
+        <v>49</v>
       </c>
       <c r="F48" s="16" t="s">
         <v>10</v>
@@ -2688,7 +2703,7 @@
       </c>
       <c r="N48" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>3,                                   0,          FLAG_SBtime,                    xxx,             xxx,                  xxx,                    xxx,             FLAG_SBtime,     xxx,                  // Clear flag FLAG_SBtime</v>
+        <v>3,                                   0,          FLAG_SBtime,                    xxx,             FLAG_SBtime,          xxx,                    xxx,             FLAG_SBtime,     xxx,                  // Clear flag FLAG_SBtime</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="15">
@@ -3527,7 +3542,7 @@
         <v>FLAG_FRACT</v>
       </c>
       <c r="N68" s="6" t="str">
-        <f t="shared" ref="N68:N96" si="4">A68&amp;", "&amp;REPT(" ",$A$1-LEN(A68))&amp;
+        <f t="shared" ref="N68:N94" si="4">A68&amp;", "&amp;REPT(" ",$A$1-LEN(A68))&amp;
 B68&amp;", "&amp;REPT(" ",$B$1-LEN(B68))&amp;
 C68&amp;", "&amp;REPT(" ",$C$1-LEN(C68))&amp;
 D68&amp;", "&amp;REPT(" ",$D$1-LEN(D68))&amp;
@@ -3548,7 +3563,7 @@
         <v>1</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>10</v>
@@ -3570,16 +3585,16 @@
       </c>
       <c r="J69" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Set flag  FLAG_DENANY</v>
+        <v>// Set flag  FLAG_MULTx</v>
       </c>
       <c r="K69" s="8"/>
       <c r="L69" s="8" t="str">
         <f t="shared" si="3"/>
-        <v>FLAG_DENANY</v>
+        <v>FLAG_MULTx</v>
       </c>
       <c r="N69" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   1,          FLAG_DENANY,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_DENANY</v>
+        <v>3,                                   1,          FLAG_MULTx,                     xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_MULTx</v>
       </c>
     </row>
     <row r="70" spans="1:14" ht="15">
@@ -3590,7 +3605,7 @@
         <v>1</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>10</v>
@@ -3612,16 +3627,16 @@
       </c>
       <c r="J70" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Set flag  FLAG_MULTx</v>
+        <v>// Set flag  FLAG_AUTOFF</v>
       </c>
       <c r="K70" s="8"/>
       <c r="L70" s="8" t="str">
         <f t="shared" si="3"/>
-        <v>FLAG_MULTx</v>
+        <v>FLAG_AUTOFF</v>
       </c>
       <c r="N70" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   1,          FLAG_MULTx,                     xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_MULTx</v>
+        <v>3,                                   1,          FLAG_AUTOFF,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_AUTOFF</v>
       </c>
     </row>
     <row r="71" spans="1:14" ht="15">
@@ -3632,7 +3647,7 @@
         <v>1</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>10</v>
@@ -3654,16 +3669,16 @@
       </c>
       <c r="J71" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Set flag  FLAG_AUTOFF</v>
+        <v>// Set flag  FLAG_PROPFR</v>
       </c>
       <c r="K71" s="8"/>
       <c r="L71" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v>FLAG_AUTOFF</v>
+        <f t="shared" ref="L71:L89" si="5">IF(NOT(C71="xxx"),C71,IF(NOT(D71="xxx"),D71,IF(NOT(E71="xxx"),E71,IF(NOT(F71="xxx"),F71,IF(NOT(G71="xxx"),G71,IF(NOT(H71="xxx"),H71,IF(NOT(I71="xxx"),I71)))))))</f>
+        <v>FLAG_PROPFR</v>
       </c>
       <c r="N71" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   1,          FLAG_AUTOFF,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_AUTOFF</v>
+        <v>3,                                   1,          FLAG_PROPFR,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_PROPFR</v>
       </c>
     </row>
     <row r="72" spans="1:14" ht="15">
@@ -3674,7 +3689,7 @@
         <v>1</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>10</v>
@@ -3696,16 +3711,16 @@
       </c>
       <c r="J72" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Set flag  FLAG_ASLIFT</v>
+        <v>// Set flag  FLAG_ENDPMT</v>
       </c>
       <c r="K72" s="8"/>
       <c r="L72" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v>FLAG_ASLIFT</v>
+        <f t="shared" si="5"/>
+        <v>FLAG_ENDPMT</v>
       </c>
       <c r="N72" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   1,          FLAG_ASLIFT,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_ASLIFT</v>
+        <v>3,                                   1,          FLAG_ENDPMT,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_ENDPMT</v>
       </c>
     </row>
     <row r="73" spans="1:14" ht="15">
@@ -3716,7 +3731,7 @@
         <v>1</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>10</v>
@@ -3738,16 +3753,16 @@
       </c>
       <c r="J73" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Set flag  FLAG_PROPFR</v>
+        <v>// Set flag  FLAG_HPRP</v>
       </c>
       <c r="K73" s="8"/>
       <c r="L73" s="8" t="str">
-        <f t="shared" ref="L73:L91" si="5">IF(NOT(C73="xxx"),C73,IF(NOT(D73="xxx"),D73,IF(NOT(E73="xxx"),E73,IF(NOT(F73="xxx"),F73,IF(NOT(G73="xxx"),G73,IF(NOT(H73="xxx"),H73,IF(NOT(I73="xxx"),I73)))))))</f>
-        <v>FLAG_PROPFR</v>
+        <f t="shared" si="5"/>
+        <v>FLAG_HPRP</v>
       </c>
       <c r="N73" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   1,          FLAG_PROPFR,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_PROPFR</v>
+        <v>3,                                   1,          FLAG_HPRP,                      xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_HPRP</v>
       </c>
     </row>
     <row r="74" spans="1:14" ht="15">
@@ -3755,19 +3770,19 @@
         <v>3</v>
       </c>
       <c r="B74" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="F74" s="16" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>10</v>
@@ -3780,16 +3795,16 @@
       </c>
       <c r="J74" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Set flag  FLAG_ENDPMT</v>
+        <v>// Clear flag FLAG_HPRP</v>
       </c>
       <c r="K74" s="8"/>
       <c r="L74" s="8" t="str">
         <f t="shared" si="5"/>
-        <v>FLAG_ENDPMT</v>
+        <v>FLAG_HPRP</v>
       </c>
       <c r="N74" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   1,          FLAG_ENDPMT,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_ENDPMT</v>
+        <v>3,                                   0,          xxx,                            xxx,             FLAG_HPRP,            FLAG_HPRP,              xxx,             xxx,             xxx,                  // Clear flag FLAG_HPRP</v>
       </c>
     </row>
     <row r="75" spans="1:14" ht="15">
@@ -3800,13 +3815,13 @@
         <v>1</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="F75" s="16" t="s">
         <v>10</v>
@@ -3822,16 +3837,16 @@
       </c>
       <c r="J75" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Set flag  FLAG_HPRP</v>
+        <v>// Set flag  FLAG_HPBASE</v>
       </c>
       <c r="K75" s="8"/>
       <c r="L75" s="8" t="str">
         <f t="shared" si="5"/>
-        <v>FLAG_HPRP</v>
+        <v>FLAG_HPBASE</v>
       </c>
       <c r="N75" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   1,          FLAG_HPRP,                      xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_HPRP</v>
+        <v>3,                                   1,          FLAG_HPBASE,                    xxx,             FLAG_HPBASE,          xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_HPBASE</v>
       </c>
     </row>
     <row r="76" spans="1:14" ht="15">
@@ -3848,10 +3863,10 @@
         <v>10</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="F76" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>10</v>
@@ -3864,16 +3879,16 @@
       </c>
       <c r="J76" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Clear flag FLAG_HPRP</v>
+        <v>// Clear flag FLAG_HPBASE</v>
       </c>
       <c r="K76" s="8"/>
       <c r="L76" s="8" t="str">
         <f t="shared" si="5"/>
-        <v>FLAG_HPRP</v>
+        <v>FLAG_HPBASE</v>
       </c>
       <c r="N76" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   0,          xxx,                            xxx,             FLAG_HPRP,            FLAG_HPRP,              xxx,             xxx,             xxx,                  // Clear flag FLAG_HPRP</v>
+        <v>3,                                   0,          xxx,                            xxx,             xxx,                  FLAG_HPBASE,            xxx,             xxx,             xxx,                  // Clear flag FLAG_HPBASE</v>
       </c>
     </row>
     <row r="77" spans="1:14" ht="15">
@@ -3881,19 +3896,19 @@
         <v>3</v>
       </c>
       <c r="B77" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F77" s="16" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>10</v>
@@ -3906,16 +3921,16 @@
       </c>
       <c r="J77" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Set flag  FLAG_HPBASE</v>
+        <v>// Clear flag FLAG_2TO10</v>
       </c>
       <c r="K77" s="8"/>
       <c r="L77" s="8" t="str">
         <f t="shared" si="5"/>
-        <v>FLAG_HPBASE</v>
+        <v>FLAG_2TO10</v>
       </c>
       <c r="N77" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   1,          FLAG_HPBASE,                    xxx,             FLAG_HPBASE,          xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_HPBASE</v>
+        <v>3,                                   0,          FLAG_2TO10,                     xxx,             FLAG_2TO10,           FLAG_2TO10,             xxx,             xxx,             xxx,                  // Clear flag FLAG_2TO10</v>
       </c>
     </row>
     <row r="78" spans="1:14" ht="15">
@@ -3932,10 +3947,10 @@
         <v>10</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="F78" s="16" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>10</v>
@@ -3948,16 +3963,16 @@
       </c>
       <c r="J78" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Clear flag FLAG_HPBASE</v>
+        <v>// Clear flag FLAG_POLAR</v>
       </c>
       <c r="K78" s="8"/>
       <c r="L78" s="8" t="str">
         <f t="shared" si="5"/>
-        <v>FLAG_HPBASE</v>
+        <v>FLAG_POLAR</v>
       </c>
       <c r="N78" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   0,          xxx,                            xxx,             xxx,                  FLAG_HPBASE,            xxx,             xxx,             xxx,                  // Clear flag FLAG_HPBASE</v>
+        <v>3,                                   0,          xxx,                            xxx,             FLAG_POLAR,           xxx,                    xxx,             xxx,             xxx,                  // Clear flag FLAG_POLAR</v>
       </c>
     </row>
     <row r="79" spans="1:14" ht="15">
@@ -3968,19 +3983,19 @@
         <v>0</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="F79" s="16" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>10</v>
@@ -3990,16 +4005,16 @@
       </c>
       <c r="J79" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Clear flag FLAG_2TO10</v>
+        <v>// Clear flag FLAG_CPXj</v>
       </c>
       <c r="K79" s="8"/>
       <c r="L79" s="8" t="str">
         <f t="shared" si="5"/>
-        <v>FLAG_2TO10</v>
+        <v>FLAG_CPXj</v>
       </c>
       <c r="N79" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   0,          FLAG_2TO10,                     xxx,             FLAG_2TO10,           FLAG_2TO10,             xxx,             xxx,             xxx,                  // Clear flag FLAG_2TO10</v>
+        <v>3,                                   0,          xxx,                            xxx,             xxx,                  xxx,                    FLAG_CPXj,       xxx,             xxx,                  // Clear flag FLAG_CPXj</v>
       </c>
     </row>
     <row r="80" spans="1:14" ht="15">
@@ -4007,7 +4022,7 @@
         <v>3</v>
       </c>
       <c r="B80" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>10</v>
@@ -4016,7 +4031,7 @@
         <v>10</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F80" s="16" t="s">
         <v>10</v>
@@ -4032,16 +4047,16 @@
       </c>
       <c r="J80" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Clear flag FLAG_POLAR</v>
+        <v>// Set flag  FLAG_CPXj</v>
       </c>
       <c r="K80" s="8"/>
       <c r="L80" s="8" t="str">
         <f t="shared" si="5"/>
-        <v>FLAG_POLAR</v>
+        <v>FLAG_CPXj</v>
       </c>
       <c r="N80" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   0,          xxx,                            xxx,             FLAG_POLAR,           xxx,                    xxx,             xxx,             xxx,                  // Clear flag FLAG_POLAR</v>
+        <v>3,                                   1,          xxx,                            xxx,             FLAG_CPXj,            xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_CPXj</v>
       </c>
     </row>
     <row r="81" spans="1:14" ht="15">
@@ -4052,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>10</v>
@@ -4064,7 +4079,7 @@
         <v>10</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>10</v>
@@ -4074,16 +4089,16 @@
       </c>
       <c r="J81" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Clear flag FLAG_CPXj</v>
+        <v>// Clear flag FLAG_FRCSRN</v>
       </c>
       <c r="K81" s="8"/>
       <c r="L81" s="8" t="str">
         <f t="shared" si="5"/>
-        <v>FLAG_CPXj</v>
+        <v>FLAG_FRCSRN</v>
       </c>
       <c r="N81" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   0,          xxx,                            xxx,             xxx,                  xxx,                    FLAG_CPXj,       xxx,             xxx,                  // Clear flag FLAG_CPXj</v>
+        <v>3,                                   0,          FLAG_FRCSRN,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Clear flag FLAG_FRCSRN</v>
       </c>
     </row>
     <row r="82" spans="1:14" ht="15">
@@ -4100,7 +4115,7 @@
         <v>10</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F82" s="16" t="s">
         <v>10</v>
@@ -4116,16 +4131,16 @@
       </c>
       <c r="J82" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Set flag  FLAG_CPXj</v>
+        <v>// Set flag  FLAG_FRCSRN</v>
       </c>
       <c r="K82" s="8"/>
       <c r="L82" s="8" t="str">
         <f t="shared" si="5"/>
-        <v>FLAG_CPXj</v>
+        <v>FLAG_FRCSRN</v>
       </c>
       <c r="N82" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   1,          xxx,                            xxx,             FLAG_CPXj,            xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_CPXj</v>
+        <v>3,                                   1,          xxx,                            xxx,             FLAG_FRCSRN,          xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_FRCSRN</v>
       </c>
     </row>
     <row r="83" spans="1:14" ht="15">
@@ -4133,10 +4148,10 @@
         <v>3</v>
       </c>
       <c r="B83" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>10</v>
@@ -4158,16 +4173,16 @@
       </c>
       <c r="J83" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Clear flag FLAG_FRCSRN</v>
+        <v>// Set flag  FLAG_CPXRES</v>
       </c>
       <c r="K83" s="8"/>
       <c r="L83" s="8" t="str">
         <f t="shared" si="5"/>
-        <v>FLAG_FRCSRN</v>
+        <v>FLAG_CPXRES</v>
       </c>
       <c r="N83" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   0,          FLAG_FRCSRN,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Clear flag FLAG_FRCSRN</v>
+        <v>3,                                   1,          FLAG_CPXRES,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_CPXRES</v>
       </c>
     </row>
     <row r="84" spans="1:14" ht="15">
@@ -4178,13 +4193,13 @@
         <v>1</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="F84" s="16" t="s">
         <v>10</v>
@@ -4200,16 +4215,16 @@
       </c>
       <c r="J84" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Set flag  FLAG_FRCSRN</v>
+        <v>// Set flag  FLAG_SSIZE8</v>
       </c>
       <c r="K84" s="8"/>
       <c r="L84" s="8" t="str">
         <f t="shared" si="5"/>
-        <v>FLAG_FRCSRN</v>
+        <v>FLAG_SSIZE8</v>
       </c>
       <c r="N84" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   1,          xxx,                            xxx,             FLAG_FRCSRN,          xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_FRCSRN</v>
+        <v>3,                                   1,          FLAG_SSIZE8,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_SSIZE8</v>
       </c>
     </row>
     <row r="85" spans="1:14" ht="15">
@@ -4217,10 +4232,10 @@
         <v>3</v>
       </c>
       <c r="B85" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>10</v>
@@ -4242,16 +4257,16 @@
       </c>
       <c r="J85" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Set flag  FLAG_CPXRES</v>
+        <v>// Clear flag FLAG_DENANY</v>
       </c>
       <c r="K85" s="8"/>
       <c r="L85" s="8" t="str">
         <f t="shared" si="5"/>
-        <v>FLAG_CPXRES</v>
+        <v>FLAG_DENANY</v>
       </c>
       <c r="N85" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   1,          FLAG_CPXRES,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_CPXRES</v>
+        <v>3,                                   0,          FLAG_DENANY,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Clear flag FLAG_DENANY</v>
       </c>
     </row>
     <row r="86" spans="1:14" ht="15">
@@ -4262,7 +4277,7 @@
         <v>1</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>10</v>
@@ -4271,7 +4286,7 @@
         <v>10</v>
       </c>
       <c r="F86" s="16" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>10</v>
@@ -4284,16 +4299,16 @@
       </c>
       <c r="J86" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Set flag  FLAG_SSIZE8</v>
+        <v>// Set flag  FLAG_DENANY</v>
       </c>
       <c r="K86" s="8"/>
       <c r="L86" s="8" t="str">
         <f t="shared" si="5"/>
-        <v>FLAG_SSIZE8</v>
+        <v>FLAG_DENANY</v>
       </c>
       <c r="N86" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   1,          FLAG_SSIZE8,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_SSIZE8</v>
+        <v>3,                                   1,          xxx,                            xxx,             xxx,                  FLAG_DENANY,            xxx,             xxx,             xxx,                  // Set flag  FLAG_DENANY</v>
       </c>
     </row>
     <row r="87" spans="1:14" ht="15">
@@ -4304,7 +4319,7 @@
         <v>0</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>10</v>
@@ -4326,16 +4341,16 @@
       </c>
       <c r="J87" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Clear flag FLAG_DENANY</v>
+        <v>// Clear flag FLAG_ASLIFT</v>
       </c>
       <c r="K87" s="8"/>
       <c r="L87" s="8" t="str">
         <f t="shared" si="5"/>
-        <v>FLAG_DENANY</v>
+        <v>FLAG_ASLIFT</v>
       </c>
       <c r="N87" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   0,          FLAG_DENANY,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Clear flag FLAG_DENANY</v>
+        <v>3,                                   0,          FLAG_ASLIFT,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Clear flag FLAG_ASLIFT</v>
       </c>
     </row>
     <row r="88" spans="1:14" ht="15">
@@ -4343,10 +4358,10 @@
         <v>3</v>
       </c>
       <c r="B88" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>10</v>
@@ -4355,7 +4370,7 @@
         <v>10</v>
       </c>
       <c r="F88" s="16" t="s">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>10</v>
@@ -4368,16 +4383,16 @@
       </c>
       <c r="J88" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Set flag  FLAG_DENANY</v>
+        <v>// Clear flag FLAG_DENFIX</v>
       </c>
       <c r="K88" s="8"/>
       <c r="L88" s="8" t="str">
         <f t="shared" si="5"/>
-        <v>FLAG_DENANY</v>
+        <v>FLAG_DENFIX</v>
       </c>
       <c r="N88" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   1,          xxx,                            xxx,             xxx,                  FLAG_DENANY,            xxx,             xxx,             xxx,                  // Set flag  FLAG_DENANY</v>
+        <v>3,                                   0,          FLAG_DENFIX,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Clear flag FLAG_DENFIX</v>
       </c>
     </row>
     <row r="89" spans="1:14" ht="15">
@@ -4385,10 +4400,10 @@
         <v>3</v>
       </c>
       <c r="B89" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>10</v>
@@ -4410,81 +4425,74 @@
       </c>
       <c r="J89" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>// Clear flag FLAG_ASLIFT</v>
+        <v>// Set flag  FLAG_SPCRES</v>
       </c>
       <c r="K89" s="8"/>
       <c r="L89" s="8" t="str">
         <f t="shared" si="5"/>
-        <v>FLAG_ASLIFT</v>
+        <v>FLAG_SPCRES</v>
       </c>
       <c r="N89" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   0,          FLAG_ASLIFT,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Clear flag FLAG_ASLIFT</v>
+        <v>3,                                   1,          FLAG_SPCRES,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_SPCRES</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="15">
-      <c r="A90" s="1">
-        <v>3</v>
-      </c>
-      <c r="B90" s="1">
-        <v>0</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F90" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J90" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>// Clear flag FLAG_DENFIX</v>
-      </c>
+      <c r="A90" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C90" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E90" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F90" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J90" s="2"/>
       <c r="K90" s="8"/>
-      <c r="L90" s="8" t="str">
-        <f t="shared" si="5"/>
-        <v>FLAG_DENFIX</v>
-      </c>
       <c r="N90" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   0,          FLAG_DENFIX,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Clear flag FLAG_DENFIX</v>
+        <v xml:space="preserve">//fnSetGapChar,                      n/a,        Reset,                          HP35,            JM,                   RJ,                     C47,             DefltSB,         TVM,                  </v>
       </c>
     </row>
     <row r="91" spans="1:14" ht="15">
       <c r="A91" s="1">
-        <v>3</v>
-      </c>
-      <c r="B91" s="1">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>10</v>
+        <v>80</v>
+      </c>
+      <c r="E91" s="17" t="s">
+        <v>92</v>
       </c>
       <c r="F91" s="16" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>10</v>
@@ -4492,53 +4500,50 @@
       <c r="I91" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J91" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>// Set flag  FLAG_SPCRES</v>
+      <c r="J91" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="K91" s="8"/>
-      <c r="L91" s="8" t="str">
-        <f t="shared" si="5"/>
-        <v>FLAG_SPCRES</v>
-      </c>
       <c r="N91" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>3,                                   1,          FLAG_SPCRES,                    xxx,             xxx,                  xxx,                    xxx,             xxx,             xxx,                  // Set flag  FLAG_SPCRES</v>
+        <v>4,                                   xxx,        0+ITM_SPACE_PUNCTUATION,        ITM_NULL,        0+_gapl,              0+ITM_SPACE_4_PER_EM,   0+_gapl,         xxx,             xxx,                  //fnSetGapChar</v>
       </c>
     </row>
     <row r="92" spans="1:14" ht="15">
-      <c r="A92" s="2" t="s">
+      <c r="A92" s="1">
+        <v>4</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E92" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F92" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J92" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C92" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E92" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F92" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I92" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J92" s="2"/>
       <c r="K92" s="8"/>
       <c r="N92" s="6" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">//fnSetGapChar,                      n/a,        Reset,                          HP35,            JM,                   RJ,                     C47,             DefltSB,         TVM,                  </v>
+        <v>4,                                   xxx,        32768+ITM_SPACE_PUNCTUATION,    ITM_NULL+32768,  32768+_gapr,          32768+ITM_NULL,         32768+_gapr,     xxx,             xxx,                  //fnSetGapChar</v>
       </c>
     </row>
     <row r="93" spans="1:14" ht="15">
@@ -4549,19 +4554,19 @@
         <v>10</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>10</v>
+        <v>87</v>
+      </c>
+      <c r="E93" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="F93" s="16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>10</v>
@@ -4575,122 +4580,54 @@
       <c r="K93" s="8"/>
       <c r="N93" s="6" t="str">
         <f t="shared" si="4"/>
-        <v>4,                                   xxx,        0+ITM_SPACE_PUNCTUATION,        ITM_NULL,        xxx,                  0+ITM_SPACE_4_PER_EM,   0+_gapl,         xxx,             xxx,                  //fnSetGapChar</v>
+        <v>4,                                   xxx,        49152+ITM_PERIOD,               ITM_WDOT+49152,  49152+_gaprx,         49152+ITM_WCOMMA,       49152+_gaprx,    xxx,             xxx,                  //fnSetGapChar</v>
       </c>
     </row>
     <row r="94" spans="1:14" ht="15">
-      <c r="A94" s="1">
-        <v>4</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F94" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J94" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="K94" s="8"/>
-      <c r="N94" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v>4,                                   xxx,        32768+ITM_SPACE_PUNCTUATION,    ITM_NULL+32768,  xxx,                  32768+ITM_NULL,         32768+_gapr,     xxx,             xxx,                  //fnSetGapChar</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" ht="15">
-      <c r="A95" s="1">
-        <v>4</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F95" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J95" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="K95" s="8"/>
-      <c r="N95" s="6" t="str">
-        <f t="shared" si="4"/>
-        <v>4,                                   xxx,        49152+ITM_PERIOD,               ITM_WDOT+49152,  xxx,                  49152+ITM_WCOMMA,       49152+_gaprx,    xxx,             xxx,                  //fnSetGapChar</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" ht="15">
-      <c r="A96" s="10">
-        <v>0</v>
-      </c>
-      <c r="B96" s="10">
-        <v>0</v>
-      </c>
-      <c r="C96" s="10">
-        <v>0</v>
-      </c>
-      <c r="D96" s="10">
-        <v>0</v>
-      </c>
-      <c r="E96" s="10">
-        <v>0</v>
-      </c>
-      <c r="F96" s="10">
-        <v>0</v>
-      </c>
-      <c r="G96" s="10">
-        <v>0</v>
-      </c>
-      <c r="H96" s="10">
-        <v>0</v>
-      </c>
-      <c r="I96" s="10">
-        <v>0</v>
-      </c>
-      <c r="J96" s="10" t="s">
+      <c r="A94" s="10">
+        <v>0</v>
+      </c>
+      <c r="B94" s="10">
+        <v>0</v>
+      </c>
+      <c r="C94" s="10">
+        <v>0</v>
+      </c>
+      <c r="D94" s="10">
+        <v>0</v>
+      </c>
+      <c r="E94" s="10">
+        <v>0</v>
+      </c>
+      <c r="F94" s="10">
+        <v>0</v>
+      </c>
+      <c r="G94" s="10">
+        <v>0</v>
+      </c>
+      <c r="H94" s="10">
+        <v>0</v>
+      </c>
+      <c r="I94" s="10">
+        <v>0</v>
+      </c>
+      <c r="J94" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="K96" s="11"/>
-      <c r="L96" s="11"/>
-      <c r="M96" s="11"/>
-      <c r="N96" s="12" t="str">
+      <c r="K94" s="11"/>
+      <c r="L94" s="11"/>
+      <c r="M94" s="11"/>
+      <c r="N94" s="12" t="str">
         <f t="shared" si="4"/>
         <v>0,                                   0,          0,                              0,               0,                    0,                      0,               0,               0,                    //END MARKER</v>
       </c>
     </row>
+    <row r="95" spans="1:14" ht="15">
+      <c r="K95" s="8"/>
+    </row>
+    <row r="96" spans="1:14" ht="15">
+      <c r="K96" s="8"/>
+    </row>
     <row r="97" spans="11:11" ht="15">
       <c r="K97" s="8"/>
     </row>
@@ -4712,50 +4649,49 @@
     <row r="103" spans="11:11" ht="15">
       <c r="K103" s="8"/>
     </row>
-    <row r="104" spans="11:11" ht="15">
-      <c r="K104" s="8"/>
-    </row>
-    <row r="105" spans="11:11" ht="15">
-      <c r="K105" s="8"/>
-    </row>
-    <row r="401" spans="11:14" ht="15">
-      <c r="K401" s="8"/>
-    </row>
-    <row r="415" spans="11:14" ht="15">
-      <c r="K415" s="8"/>
-      <c r="N415" s="7" t="str">
-        <f>"  "&amp;B415&amp;", "&amp;REPT(" ",$BH$55-LEN(B415))&amp;
-C415&amp;", "&amp;REPT(" ",$BH$55-LEN(C415))&amp;
-D415&amp;", "&amp;REPT(" ",$BH$55-LEN(D415))&amp;
-E415&amp;", "&amp;REPT(" ",$BH$55-LEN(E415))&amp;
-F415&amp;", "&amp;REPT(" ",$BH$55-LEN(F415))&amp;
-G415&amp;", "&amp;REPT(" ",$BH$55-LEN(G415))&amp;
-H415&amp;", "&amp;REPT(" ",$BH$55-LEN(H415))&amp;
-I415&amp;", "&amp;REPT(" ",$BH$55-LEN(I415))&amp;
-J415&amp;REPT(" ",$BH$55-LEN(J415))&amp;
+    <row r="399" spans="11:11" ht="15">
+      <c r="K399" s="8"/>
+    </row>
+    <row r="413" spans="11:14" ht="15">
+      <c r="K413" s="8"/>
+      <c r="N413" s="7" t="str">
+        <f>"  "&amp;B413&amp;", "&amp;REPT(" ",$BH$55-LEN(B413))&amp;
+C413&amp;", "&amp;REPT(" ",$BH$55-LEN(C413))&amp;
+D413&amp;", "&amp;REPT(" ",$BH$55-LEN(D413))&amp;
+E413&amp;", "&amp;REPT(" ",$BH$55-LEN(E413))&amp;
+F413&amp;", "&amp;REPT(" ",$BH$55-LEN(F413))&amp;
+G413&amp;", "&amp;REPT(" ",$BH$55-LEN(G413))&amp;
+H413&amp;", "&amp;REPT(" ",$BH$55-LEN(H413))&amp;
+I413&amp;", "&amp;REPT(" ",$BH$55-LEN(I413))&amp;
+J413&amp;REPT(" ",$BH$55-LEN(J413))&amp;
 "},"</f>
         <v xml:space="preserve">  , , , , , , , , },</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K1:M1">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>$M$1&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L1:XFD1 A1:J1048576 L2:M96 O2:XFD96 L97:XFD414 L415:M415 O415:XFD415 L416:XFD1048576">
-    <cfRule type="containsText" dxfId="2" priority="5" stopIfTrue="1" operator="containsText" text="xxx">
+  <conditionalFormatting sqref="L1:XFD1 L95:XFD412 L413:M413 O413:XFD413 L414:XFD1048576 L2:M94 O2:XFD94 A1:J1048576">
+    <cfRule type="containsText" dxfId="3" priority="6" stopIfTrue="1" operator="containsText" text="xxx">
       <formula>NOT(ISERROR(SEARCH("xxx",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N96">
-    <cfRule type="expression" dxfId="1" priority="3">
+  <conditionalFormatting sqref="N2:N94">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>ISNA(N2)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N415">
-    <cfRule type="expression" dxfId="0" priority="4">
-      <formula>ISNA(N415)</formula>
+  <conditionalFormatting sqref="N413">
+    <cfRule type="expression" dxfId="1" priority="5">
+      <formula>ISNA(N413)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:XFD1048576">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="_HP">
+      <formula>NOT(ISERROR(SEARCH("_HP",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
